--- a/Excels/GameData.xlsx
+++ b/Excels/GameData.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devs\TRPG.Client\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF804BF-B476-4D17-AC18-09E8F6EA19DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B54BC5-C7FF-47C2-8CE2-2D644C056C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{4C3ECC9E-3FC4-471E-A1D2-0D99937C0D65}"/>
   </bookViews>
   <sheets>
-    <sheet name="MonsterData" sheetId="1" r:id="rId1"/>
+    <sheet name="CreatureData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Damage</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>쥐</t>
-  </si>
-  <si>
-    <t>PF_Monster_00</t>
   </si>
   <si>
     <t>Attack_00</t>
@@ -75,10 +72,6 @@
   </si>
   <si>
     <t>Hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PrefabAddress</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -638,33 +631,30 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" thickBot="1">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="18" thickBot="1">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>3</v>
@@ -672,20 +662,17 @@
       <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="5">
+        <v>10</v>
+      </c>
+      <c r="E2" s="5">
         <v>5</v>
       </c>
-      <c r="E2" s="5">
-        <v>10</v>
-      </c>
       <c r="F2" s="5">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>5</v>
-      </c>
-      <c r="G2" s="5">
-        <v>1</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="18" thickBot="1">

--- a/Excels/GameData.xlsx
+++ b/Excels/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devs\TRPG.Client\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B54BC5-C7FF-47C2-8CE2-2D644C056C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0E4C97-7593-4B01-BA53-255D9D666B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{4C3ECC9E-3FC4-471E-A1D2-0D99937C0D65}"/>
   </bookViews>
@@ -666,7 +666,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2" s="5">
         <v>1</v>

--- a/Excels/GameData.xlsx
+++ b/Excels/GameData.xlsx
@@ -2,44 +2,40 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devs\TRPG.Client\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0E4C97-7593-4B01-BA53-255D9D666B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D45395-3D94-43B2-B5C1-ECABDB9E90F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{4C3ECC9E-3FC4-471E-A1D2-0D99937C0D65}"/>
+    <workbookView xWindow="30984" yWindow="3360" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>DisplayName</t>
+  </si>
+  <si>
+    <t>MoveRange</t>
+  </si>
+  <si>
+    <t>DefaultSkillId</t>
+  </si>
+  <si>
+    <t>Hp</t>
+  </si>
   <si>
     <t>Damage</t>
   </si>
@@ -50,6 +46,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Monster_00</t>
+  </si>
+  <si>
     <t>쥐</t>
   </si>
   <si>
@@ -59,24 +58,7 @@
     <t>더미 몬스터</t>
   </si>
   <si>
-    <t>Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DisplayName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DefaultSkillId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monster_00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>King</t>
   </si>
 </sst>
 </file>
@@ -88,34 +70,28 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Google Sans"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF434343"/>
       <name val="Roboto"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움체"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="4">
@@ -128,13 +104,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF356854"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -261,25 +235,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -300,7 +274,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -342,108 +316,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -451,80 +331,31 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -554,22 +385,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -584,98 +415,79 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{358137F3-7CA8-47CB-A8E5-C0614277455D}">
-  <dimension ref="A1:H3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="15.59765625" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="29.69921875" customWidth="1"/>
-    <col min="4" max="4" width="19.69921875" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="8.8984375" customWidth="1"/>
-    <col min="7" max="7" width="13.8984375" customWidth="1"/>
-    <col min="8" max="8" width="71.5" customWidth="1"/>
+    <col min="2" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="29.69921875" customWidth="1"/>
+    <col min="5" max="5" width="19.69921875" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="8.8984375" customWidth="1"/>
+    <col min="8" max="8" width="13.8984375" customWidth="1"/>
+    <col min="9" max="9" width="71.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" thickBot="1">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="18" thickBot="1">
-      <c r="A2" s="4" t="s">
+      <c r="C2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="5">
+      <c r="E2" s="5">
         <v>10</v>
-      </c>
-      <c r="E2" s="5">
-        <v>1</v>
       </c>
       <c r="F2" s="5">
         <v>1</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>5</v>
+      <c r="G2" s="5">
+        <v>1</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18" thickBot="1">
+    <row r="3" spans="1:9">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -684,10 +496,15 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="C2:C100" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"King,Queen,Rook,Bishop,Knight,Pawn"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>